--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.21577568229495</v>
+        <v>2.79756354837293</v>
       </c>
       <c r="D2" t="n">
-        <v>21.02499408250237</v>
+        <v>3.416561538406635</v>
       </c>
       <c r="E2" t="n">
-        <v>18.8277479675263</v>
+        <v>3.059509044723023</v>
       </c>
       <c r="F2" t="n">
-        <v>17.76447944906985</v>
+        <v>2.886727910473851</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.40819313281404</v>
+        <v>6.728831384082282</v>
       </c>
       <c r="D3" t="n">
-        <v>41.06604816778227</v>
+        <v>6.673232827264619</v>
       </c>
       <c r="E3" t="n">
-        <v>18.8277479675263</v>
+        <v>3.059509044723023</v>
       </c>
       <c r="F3" t="n">
-        <v>17.76447944906985</v>
+        <v>2.886727910473851</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.35345775721987</v>
+        <v>3.144936885548228</v>
       </c>
       <c r="D4" t="n">
-        <v>19.60588240809375</v>
+        <v>3.185955891315235</v>
       </c>
       <c r="E4" t="n">
-        <v>18.8277479675263</v>
+        <v>3.059509044723023</v>
       </c>
       <c r="F4" t="n">
-        <v>17.76447944906985</v>
+        <v>2.886727910473851</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>63.57234615899527</v>
+        <v>10.33050625083673</v>
       </c>
       <c r="D5" t="n">
-        <v>63.2737924651958</v>
+        <v>10.28199127559432</v>
       </c>
       <c r="E5" t="n">
-        <v>18.8277479675263</v>
+        <v>3.059509044723023</v>
       </c>
       <c r="F5" t="n">
-        <v>17.76447944906985</v>
+        <v>2.886727910473851</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
